--- a/data/trans_camb/P1802_2016_2023-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1802_2016_2023-Habitat-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,34</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,15</t>
+          <t>-2,53; 4,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,1</t>
+          <t>-4,55; 2,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,34</t>
+          <t>-2,63; 2,75</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-1,56%</t>
+          <t>-3,11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 48,16</t>
+          <t>-16,45; 44,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 20,59</t>
+          <t>-23,85; 19,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 25,11</t>
+          <t>-16,13; 20,12</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15,04</t>
+          <t>-3,4</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-6,26</t>
+          <t>-5,8</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>-4,61</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 49,36</t>
+          <t>-6,36; 0,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -3,07</t>
+          <t>-9,36; -2,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 31,16</t>
+          <t>-6,82; -2,3</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>-21,02%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-30,42%</t>
+          <t>-28,15%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>-25,05%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,02; 299,87</t>
+          <t>-36,02; 2,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,3; -16,26</t>
+          <t>-41,07; -15,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 182,15</t>
+          <t>-35,06; -13,53</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-4,52</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,1</t>
+          <t>0,24</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 4,38</t>
+          <t>-3,73; 3,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 0,94</t>
+          <t>-2,83; 4,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 1,26</t>
+          <t>-2,46; 2,79</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>-2,75%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-23,7%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,7%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 35,62</t>
+          <t>-23,2; 28,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-59,09; 5,0</t>
+          <t>-13,19; 27,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,38; 7,97</t>
+          <t>-13,5; 18,1</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,88</t>
+          <t>5,86</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>4,89</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,44</t>
+          <t>2,13; 9,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 7,46</t>
+          <t>1,67; 8,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,84</t>
+          <t>3,08; 7,71</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,93; 85,35</t>
+          <t>13,41; 77,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 46,66</t>
+          <t>8,69; 50,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,27; 52,88</t>
+          <t>17,34; 51,9</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-1,7</t>
+          <t>-0,13</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 25,54</t>
+          <t>-0,88; 2,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,43</t>
+          <t>-1,81; 1,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 13,81</t>
+          <t>-1,02; 1,48</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-8,99%</t>
+          <t>-0,7%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,26; 187,07</t>
+          <t>-5,78; 18,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 2,33</t>
+          <t>-9,08; 8,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 86,93</t>
+          <t>-5,73; 9,3</t>
         </is>
       </c>
     </row>
